--- a/building_inspector_forms/003_septic_inspection_form--building_inspector_forms.xlsx
+++ b/building_inspector_forms/003_septic_inspection_form--building_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'multi'}</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Multi'}</t>
+          <t>Multi</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_installed'}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Installed'}</t>
+          <t>Not Installed</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_1000_gpd'}</t>
+          <t>less_than_1000_gpd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 1000 gpd'}</t>
+          <t>Less than 1000 gpd</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'1000-2000_gpd'}</t>
+          <t>1000-2000_gpd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '1000-2000 gpd'}</t>
+          <t>1000-2000 gpd</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'2000-3000_gpd'}</t>
+          <t>2000-3000_gpd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '2000-3000 gpd'}</t>
+          <t>2000-3000 gpd</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'3000_gpd_or_more'}</t>
+          <t>3000_gpd_or_more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '3000 gpd or more'}</t>
+          <t>3000 gpd or more</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_inspected'}</t>
+          <t>not_inspected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Not Inspected'}</t>
+          <t>Not Inspected</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'semi-annual'}</t>
+          <t>semi-annual</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Semi-Annual'}</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
